--- a/output/pdf_financials_xlsx/WCSB.xlsx
+++ b/output/pdf_financials_xlsx/WCSB.xlsx
@@ -929,22 +929,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000508</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000643</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-2.2e-05</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001684</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.001822</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -1699,22 +1699,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.8572610000000001</v>
+        <v>-0.856761</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.445822</v>
+        <v>-0.445314</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.07714600000000001</v>
+        <v>-0.076503</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.476556</v>
+        <v>-0.476534</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.20045</v>
+        <v>-0.202134</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.524157</v>
+        <v>-0.525979</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1799,22 +1799,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.8572610000000001</v>
+        <v>-0.856761</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.445822</v>
+        <v>-0.445314</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.07714600000000001</v>
+        <v>-0.076503</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.476556</v>
+        <v>-0.476534</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.014869</v>
+        <v>0.013185</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.373454</v>
+        <v>-0.375276</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-427.9137444779994</v>
+        <v>-427.6641625277659</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-214.6853315227075</v>
+        <v>-214.4407044105113</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-86.03707090759039</v>
+        <v>-85.31996520420226</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-147.2064942406242</v>
+        <v>-147.1996985169878</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1.959846154251715</v>
+        <v>1.737882274787065</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-47.31182523253428</v>
+        <v>-47.54264923113565</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -2028,19 +2028,19 @@
         <v>0.002849</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.043372</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.704218</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.219124</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.041474</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.066715</v>
       </c>
     </row>
     <row r="35">
@@ -2116,19 +2116,19 @@
         <v>0.017063</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.043372</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.704218</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.219124</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.041474</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.066715</v>
       </c>
     </row>
     <row r="37">
@@ -2644,19 +2644,19 @@
         <v>0.076852</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.043372</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.929052</v>
+        <v>0.224834</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.457684</v>
+        <v>0.23856</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.284909</v>
+        <v>0.243435</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.40036</v>
+        <v>0.333645</v>
       </c>
     </row>
     <row r="49">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -28614,7 +28614,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -29255,7 +29255,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E328" s="5" t="n">
